--- a/lab3/1.xlsx
+++ b/lab3/1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A59A41F-00C7-4B2C-8416-F94CC446A49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B911DE1E-70B0-4FFD-A252-D6FD8FDDEDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>

--- a/lab3/1.xlsx
+++ b/lab3/1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\OPD\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B911DE1E-70B0-4FFD-A252-D6FD8FDDEDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -228,7 +227,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -561,17 +560,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
-    <col min="4" max="4" width="28.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,7 +587,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -596,7 +595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -607,7 +606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -618,7 +617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -629,7 +628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -646,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -663,7 +662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -680,7 +679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -697,7 +696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -714,7 +713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -731,7 +730,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -748,7 +747,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -765,7 +764,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -779,7 +778,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -793,7 +792,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -807,7 +806,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -821,7 +820,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -835,7 +834,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -843,7 +842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -851,7 +850,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
